--- a/dataset/kobert_ner_sample.xlsx
+++ b/dataset/kobert_ner_sample.xlsx
@@ -5,260 +5,350 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이상규\Desktop\OSP-TEAM37\dataset\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이상규\Desktop\OSP-TEAM37\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18940" windowHeight="6290" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="8380" windowHeight="6260" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="kobert_ner_sample" sheetId="1" r:id="rId4"/>
+    <x:sheet name="kobert_ner_sample_with_ocr" sheetId="1" r:id="rId4"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="110">
+  <x:si>
+    <x:t>ANUA) Gapnsaiyes} 터시 매596 내륙화 1000 연인정보 304 태시고기 IIO) T? TILY 0029 -:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>open 중 a 굶 i @ 낙 고 옆 사 '7 유 야 팩 7 출 모 탓 푹 못 # 무 흙 뼈 틈 초고y 품 조집 무기 Chd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직품유히 건다하| 내용히 509 그리l어저 %교운ml 부부백; 콤어 위요-문-흥l l _인 안생로 7길 ? [흉목보고로200V @ 3 소비기한 {우면 표기일까지 잘리린 0 [로궁l륭 물히 올리고등-사고동- 353 #섯리먹탄? 2 오도-철제, 산도조절제2 산도중적제? [졸- 불전적일하지겹다 }문유지강3요 롭_ 심장속소 청제수 시자항색소. 대두 땅공 흔입가능 '직사콤_물 피양여 호도  은 '중안 대두 요공 동록 '급적 불러듯집시용 그관 및 반문 본시고_상담실 및 신고논 야므l 신공호다 '번없이 1399 과랑 접심지 4 내설신 60 9 160 Kcal 15 05 25 소비동 영a밥 온입재제 프리 돼지고기.위 중말 유증송이  소비사 영업스  @ 이래 : 58 75 닐9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>k'세곰 나의티타임 달린미 E입 소자 슈* 함께 튼튼안다 '위만 휴세 @hocl?3 CSOSOO m P리 [모집지심다리 UO무리 330 1각터 기소치루 대한 79표7 (사시1 서로 '신지분위-지나드썹) 오 히가긴 리 코선이버 신어 의' 아예 미계 피내부 느세요 장'" 메이트 커뻐; po트 '이침까지 요골 FZSU-ITI DS 영양장보 {식찮미 a하: 바가 Igt6Dsatoo'u7 신국보 고번소 ~"리산-김 식8생유시만다이시야신) 주오리 보수3보 쇠지 @ 신비서20 '그O베다 용 A l6o</x:t>
+  </x:si>
+  <x:si>
+    <x:t>린0 말리 기타 댁린 힘유 @로움점일행 한천 '힘유제 조건제어모제베진로생승 %) (8959% l출 다요시설사트 일일길숲 플발콤플해탓 @혼고등 국번 M개류물전부 홍합 또 보심 가능 부덤 및 l사관신올 피하여 실문 텅각 '제조권 G5 산도조질제] P고"' '536 스고 {감미료) 식용유지가]품 산도조절제? 되지고기루송야 복숨이능-액 당알코올 171 D 말리돌 '알코올말터늄액  있습니다 '고등어계점; , "ui자kdy 모람) 잔 신고 교다 CtA 묻람식문 3311 반조 '고개지경센터 (070)4637 2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 대두, 우유, 땅콩, 달걀, 쇠고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐디뱀내하항 50 "훨8 ll음로 무중입지올유화 /물t 구1 [유등런문 -대인 (주크리운제과 전북자빌자지도 군섭 서주무드주P공질 소비기인 후면 표기일까지 짙리 소비션 땅 물없 올리고당; '중아놈 -데? 항되복숨이 #감미되 현 신도조절제 _ 산동중질 고전행) 기타스용우-기 필중야 소 불중이용3 똑중아항 ; [지고기 복승하학 버리주스 유화재 달걀 호두 밀 햇밀 영콩 4 J물움움유 망6어고기 록말록지증-콤무양 [률이용고 [한P5고기 오정어 엇기루다_ 조식 신불피하영 온도 [그시설서 저조하고 있습니다: '드십시오 패보전해 주요고 봉후 가급적리 및 영업_ 물은 의만 피해보상 교환 및 반품 론사고객앉다히말 고객상담실 엎출품 {@주 @  표꿈 과랑 부정 운n직품 진고는 국번없이  O 내용립 50 01 160 kcall 27 2017048457793 품목보 고 '고등어고지의 표기 7도 소비다 담080-109 섭저지 '안속니다 26 2 움망점보 WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-SOY|B-MILK|B-PEANUT|B-EGG|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|B-PEANUT|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_133936_jpg.rf.e976887593a5dfdee0dfd24c75ea13b1_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_133930_jpg.rf.936283b369c239e4469cfafd88abcacd_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133627_jpg.rf.9229bc83ef7c2ce234bb6c908a7bb049_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133646_jpg.rf.d1d156215bc8d75c50e0fed0cff8aa62_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133650_jpg.rf.42e201bf877c5ec52e99d6d2f3c8e863_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133831_jpg.rf.3327be8e6ebb2ddcae58f556d7acce68_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133722_jpg.rf.36af60d9cafeb74cd30a3850599b1e0f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133634_jpg.rf.753889fd0fce8764aa39121ac9f18adb_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133836_jpg.rf.a82fbd4a8e62434e4006243ba19956e3_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133848_jpg.rf.604060740d2b62c4a27514dd5db2ea45_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133820_jpg.rf.f79bf52bfa23b06661c8bcd71e3817e9_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133621_jpg.rf.c3887d6390bc4eff5679dbf75a4cc8d5_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134101_jpg.rf.31291d284c56619b567920454c551aef_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134912_jpg.rf.fa9ad12d1b6eec77586399144cf94d52_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133330_jpg.rf.de69efcddb15777fe221234b7399ec90_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133643_jpg.rf.6c69f3e3051a0711e1d9fcd9ae05ec32_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134056_jpg.rf.7dbf04349226ca02326439c8cb63cfd8_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133344_jpg.rf.e48cc88355eed51e52467cc0af78e13b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133826_jpg.rf.1f05c7afad87c834729c4e69cf60ba12_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133638_jpg.rf.96aeb186d920b46a12a704fece16edd0_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133656_jpg.rf.00a7cd51b1bc8474210a809df52eaac7_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133327_jpg.rf.6ad8b7bc052fe267dc6cb186f362f394_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134044_jpg.rf.3f10895ccad6ea809c916ccbf47d337d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134258_jpg.rf.b5b5e0a48f4851716aefd7995d3e7d70_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134750_jpg.rf.e796a2b61a281428b46f40cd451e9482_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133326_jpg.rf.4f05b90e1231f0a37a569ad728219b9b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_135034_jpg.rf.fce49c5fd42aff4cf8d899b8ab9138c2_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133355_jpg.rf.932836217ffce9ecc65bb050612f908f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133353_jpg.rf.5e6f59227143fff9dbf806cfac7fad26_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133608_jpg.rf.ce798d41b7948148205776e62f76ac1d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ocr_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>image_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|대두|계란|우유|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|우유|대두|땅콩|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기, 복숭아 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기|토마토|복숭아|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7 4 h진 무 너대 ; [활@ 2 "주려주스 중행 9 '유유하 잔 용 이 지온 '오. 제 70 오 'T 개용 곳대 보관해 모생 F ' [ 내기보상 바고 그_품신교 ( [명양청보 160 MI 7 I 낱p필 욕 문미 1339가) 유 계 "Vun s 7무보: 9a히) 설다 포기의 신망다 '맨 (소바기다 '올리고  "신도조실? 'ga안 '산도조질제 ` '"중 거i 보 k료 "복숨083 [감이회 : '복숨082 '물잘오다 '유 도모 '피하다 폐고기도 {조리국튼 5오 직량 살이다- ; 가_ 매_OL 시용산무 [제조하고 ' 자조시서 (주시고 '(서용979 은 '7 경식품 내끝니 377 KCI 새</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CKOWN TI Sigran&amp; 도 RUlBIlRGCOIII 기으 끓미의 F 플 바x시니처 불런드 운산 C( 앞영 이미N에 너거린 219 8" 소I 소비기신 만기_끼기 엉양정보 NU N뇌 37 kcal 그스 커피 미(지t기이 "미 ""새" '리n '시다 '미7대 고기 미과 I09팀 가스L ATAIISI 소속 '증기 대무구 신@-T" "7 " 소끼시 {w리이지이신 ,미a 무 나SU IWmn M키만 마르다' 계자 ;재끗자품-a 자? UUI 고녀이시다신 'n)lt 6비 [n대 기터가리히 _가계 시미 d점9 틈 플_패손t # 어리오리야산 m0  무하자 언제 NUn 가미 어기뻐터 가모니지 'V2d ToI 다스지다하7 잎: 피지:2u 시교 입사 @ 7색   ? 고요두문  y인소 스모 구입나 FL신 휴 깨어고 9 나으; Be9 되-꽤어 왜 U UI 뇌' 신a 비리Oln) '인 어고하다 [라s '내 이다 IX II '거W) 쿠르다스 커피 Olend 3eA Ue 가괜리{ # -가 ITI ( 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{ 출 환통 EIDSICal [원질보 IIV 틀 Vu 70 42 운안: - ; 7 { 틈 통 총 = 흙 = 총 [ 도 틀 OEH 출 비"g] u v';NA 터t:] 구 c6 " 부벼 V'a otovo 무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 9 COUU 1apan미 퍼지문지리_; 소비기래 이신 '리사리지밥산-- 수입 판대인 스배: 질로-품물주 료록집주_로립하문@ 도S 백신당-플옥주수전다; 플도 텍스트렉 포도관 '전진자현문 쫓대 물관 개품 후가금적 시E님 '피해보장 피해 및 구입간 미어 미합 399 문저: 본 스신수 국번없이 무전 '깨끗히  'o시젠트 보미는 2 듯 모 푹 쇼 ("우 'Rer OaIOMFODD 메주- 주오리2 그리세린사렉신예 [감치하테이크기(김자, 요소제 신도소럽제2 ~리리 E요 구연산]. '민길자맛분만 '실제소금 습뇨가 시O성크림 '직사찮신, 있습니대 안심히고 신고 이므로 , 굉팅식문 반심은 ZII 초23 편집 TK Chocrip 기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아리보 드어린 여3,정다 세 M표8 일, 우유m '@안 제 기은 세조시 Y예서 메조히고 미l니다 J268 kcal) 라드 긍성거래히 언쥐 교사 모생대리 기본어 이거 표시적의 | 실꺼기 '면 맡T 수 ^ 3나 기 무껑 김 식8 신고' 겁가노 국두 하이 1399 제3 내 입쓰덩어리가 간국실 70 '권립 수 있으u 미는 제즈? 9예 검계수 서 사용다 식장터분이 군어&lt; 구업 으도 인사예 유해하니 제거 $ 바거로연 영입U보 u83 800 268) Ug급딩 |말 @입 청_ 기O내 다르 @수의요 627 고기 도이도 목숨이 입 에 지반 Oa 3UA 트대 N멘 0 모화시망 0 Omio '50 Ue [표 113055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|대두|우유|땅콩|달걀|쇠고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-WHEAT|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RABO Grlpeftur 하리보 자목 책리 100 ((310 R J 의세 1 메께지 1333 하업 썰리사 설기다 399 공지밥다 새개길 70 "21578 _ 더시F 어신 무바무신 제기 주드시관 구민 '심합로 엘어베리 엉입경보 UBfime 33 UB BMMII  (U법 내5;   IOmng 급수되다 B70 입위 답; 0 지붕 Og 가리 Vg Us 0g (BOTu GNA A OI 0s 0s "0016 탑 바입니 차8? 거거런드 n Com harlbo NWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"II Mm @H UoRuvo (3 ZoVR 시우얘 U 새밥화 밑 우부 '시B반 제법 U5 까도하고 옛7니다 60 G?Bd C에) 문 제무은 관접 고시 년 몹시a 입까지바 VFORLO 연 (티길 0? 0-8363 굽시다 연양정보 uTa OMIV FN Nu 소고기 입유 bNI 원산지 Kurmi Comw harlbo; WWW 터키</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@ 아도: 이리덕 @움 눈씨니 얼굴 #Q로 가꾸_a P  내gD Ii0 Io9 1당류022 U2pral 미0D시 08 TU 2DNC @_이멘로 runrorhoulCo Ld '수입원 신n로 'NA'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(ARUBO) Ii " li "MI-S 하리보 프루티부시 두미주 이 바리보 아S 꼬다' 10D KCal) 메 개민 표사점 #이싸기 바가다 는 리 3중프리지 78 시 02-5/8-0385 17연신 "5 시대 V3 M입 끼0 Gerivo) W0O p 가꾸다 WOOI디 자고기 이터 '01340 '김기5 새꺼거 곤미입 '376(2 '리0 N햇 Doroso yorttoo WWW 닫;^</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-SOY|B-EGG|B-MILK|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인식 불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|달걀|우유|대두|복숭아|돼지고기|쇠고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기, 토마토, 복숭아 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 대두, 계란, 우유 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OOI Muamd Tryuliiors 09 Dpnilina Iarti Uonna 교4 poslor Oumulise( 4m wo) Wheat Soteawoylom dimiT SmnAS MikzNnavulloy 600Fax 2I2 ";어 거없0 UI '리가 미어 '다I 3 '대터니다 영양징보 098 BIO 입 ou oity K9 AyD' (Naiai]) ODa +90 구UU M 0 1.Xw O/vu 'n기 Gom 'horlbo WWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00 8  3 '어쨌리? 눈말 40 셋 233 (행점 '의한 유 힘 8 '7후리로L보 6 명 758 % ASI23tzgyligrg oTDDSU2 (생포로사 올리기유 조릿공품 '유화지 5린 학심 [가공유제경의유) 비E오다 17399. 냄저 '소비지기밥벌다 요이다 [명양정보 62876 '지도함위 LmPI '직장선및 y시고L Ia 내L꾸다 {보움 [물E 내용량 Doo피 EmDal Ey배Og 349 190 kcal I5q 'B0SX [`기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 대두, 쇠고기, 토마토, 달걀, 호두, 밀, 메밀, 땅콩, 고등어 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라pa;^ 소컷끼이 5I 가 IS 5 I AIil 98na4드새} Ooh 조미기 149 김수시하다? '오리온 (주공장 비림 주 스지 둘멋 학수 '3중 식S i집망고 '식물' 발들T스트레 음@ 말 구언산  "필말 대로 텅 구모저 해j 방움 흉업떼= 재후 개 1399 부정 "l 릭=트 평콩; 의한 불로기통 '책장 둘하올다 곳 본사말 '반문치' WI 망고리싸다? 구 { 1ena 8 SUI 어씨 8베5 경정보 I0m 가너U)기 모심재심 '식3청으치다 직출유교 | 밀리  사가" {립불/인요 효심복도 '밀리미시야산; '근래 소비담유 또도망 요거트분길, 0-소비물먹 물치로유 소르비단지방산-스크리 산도조전제 전끗 '예트님신 ; 문말유크림 #E미3 물린 상우지2 {방산계스템로 백설탕; 국N고기 '이스라결산 온함제제키변성전문 , 성문사 물리리지등 'S입제-3식물 (농춧무데' '꽂로필런리룹 '비져나농죽분등 행료제제방료 집입가등 '비라물태 Biiy HO '-카로켓칙색로 초료출 'Biim [0리비야켓 'z없이 (혼합제체식물성유자 9요 오징업 '불랑식품 닮고기 토미토 '피해보상 호두 '기본번에 "습도가 낮은 소비자 511253 - Ioym   c-등c장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-SOY|O|O|B-EGG|O|B-WHEAT|O|B-PEANUT|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J론풍 E: 글느; I8 9r Z9 겨y C 터거 803보 09goo 268/C @기0I60U n리 IA 091 Grrg Ge 서구하4"38531 8스경= 269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>162 9 남약 매주시 coN 밀 인 애 d 엿땅 98.7 % 청제소금식물 마 [원재료명크림액 부 도덤 수소암모는 데 (설탕 제 트 따안유 스 미 k 건_ 보관방법 대로 671 수대 '반 터 보관시 시 도 이 접실 (위#' 사 대 의기 이 (망 p' 이 ^ 내용량 고구마형기지 [과사(유탕처리제품) 제며명 경기도 (주)코스모스제과 (식품뉴영 960번길다 금강로 진접움 (옆하다 CSmnS (http llwWW 후면표기일까지 '판울래 캐나다)] 소비기한 '가루[밀(미국 '유표올레인유(말레이시야산)| 토코메물(혼합형)] 당류가공품 콩비터(인도네시야신 [명 Potmto 스타 '글리세라지방산에 물 '생어노로로제 '양파액기스CM 코고아블 스6; 말투 (간미 [뽑안 곳예 '바로 '리에터레(내 4113 11986033205148 OBo 국심상 치하 ? 실해 세a 구입지 주의시입 선쥐 기다 (기뻐 통</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|밀|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그회 어리거 S 느 P어 영0 보 UBV 600 268 088818 ' 기;이다 Smo O뇨 NS 0a 스지다 09 09 OmnO 57 uo 4653 VeoI UJizw OL 5332 Anlae Cad :어9s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥스다 K 09 이 mI [H 소 O 이 (O 6 거개  기) 25까지 2026, N리INa WN '제Iila GM 입소입 기인N 소새N Ved OOaliBokCa '(0EN 'io 109 없새요버 06 'Noll</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두, 아황산류 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두, 땅콩 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제품명 : 권더 조골핏 쿠리이이이 식품유형 : 준조클렉 이야기락 총 우유성분 : 3396. 충 코코야인로 1393 원재료명 : 밀크조골렉 4096 (설탕 전지분유 우리마이 0 코코아버터 코코아매스 레시린 향료 이어기만 (바닐린향)) , 설탕, 탈지분유 식물성지방 무수유지방 레시린 향료바닐리향) Oe 알레로기 정보:우유 대무 합유 제조원 Ferrero FoodlHangzhou) Co Lid QR코드스랜무 어플레이두다운로드 수입원 : 폐레로 아시야 리미티드 한국지점 STORY 이일랜드록선댁 (반물교환업무 소재지: 경기도 평택시 진위면 진위서로 63) 판매원 : 매일유업주) 경기도 우리아이외 함께다양한이야기블 평택시 진위면 진위서로 63 직사장선들 단들고 위고 또든어보세요 피해 건조하고 서늘한 곳에 보관 톤 제품은 그라-기 로야 코다; 스" 컴우 2시간 공정거래위원회 고시에 의거 고환 또는 보상 미다-기 이미데당 모이서새국_이야기념 받울 수 있습니다 부정: 불량식품 신고는 수입주L다 5PPO 느 이33053 업애 미미미심 수 국번없이 1399 고객상담실 : 1588-1559 하다 반품 및 교환 : 구입처 및 수입원 영양정보 내용량 509 284kcal 나르문 615rig 39이 | 탑수화물 2720 8%| 당류 26.79 2796  지방 1759 328 트랜스지방 029 포화지방 1139 759 콤레스템물 175mg 66 단백질스49 896 갈술 I5Omig 21% 인 1225ma 18*6 1 영입성분 기준기언 대한 비어찌은2@아m 기준이므로 개인의 밀교 입림에 미라 힘글니다 8017"7609 원신지; 중국 소비기합(입원년 까지) 옆면 표기 상상이 재f는</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unreadable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>readable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기|복숭아|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 돼지고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|돼지고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|대두|함유</x:t>
+  </x:si>
   <x:si>
     <x:t>밀|우유|대두|함유</x:t>
   </x:si>
   <x:si>
-    <x:t>우유, 대두, 쇠고기, 토마토, 달걀, 호두, 밀, 메밀, 땅콩, 고등어 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|대두|함유</x:t>
+    <x:t>우유|대두|쇠고기|토마토|달걀|호두|밀|메밀|땅콩|고등어|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 달걀, 우유, 대두, 복숭아, 돼지고기, 쇠고기 함유</x:t>
   </x:si>
   <x:si>
     <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O|O|O|O</x:t>
   </x:si>
   <x:si>
-    <x:t>밀, 달걀, 우유, 대두, 복숭아, 돼지고기, 쇠고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|대두|쇠고기|토마토|달걀|호두|밀|메밀|땅콩|고등어|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-MILK|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_133936_jpg.rf.e976887593a5dfdee0dfd24c75ea13b1_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_133930_jpg.rf.936283b369c239e4469cfafd88abcacd_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133627_jpg.rf.9229bc83ef7c2ce234bb6c908a7bb049_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133646_jpg.rf.d1d156215bc8d75c50e0fed0cff8aa62_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133650_jpg.rf.42e201bf877c5ec52e99d6d2f3c8e863_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133831_jpg.rf.3327be8e6ebb2ddcae58f556d7acce68_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133722_jpg.rf.36af60d9cafeb74cd30a3850599b1e0f_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133634_jpg.rf.753889fd0fce8764aa39121ac9f18adb_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133836_jpg.rf.a82fbd4a8e62434e4006243ba19956e3_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133848_jpg.rf.604060740d2b62c4a27514dd5db2ea45_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133820_jpg.rf.f79bf52bfa23b06661c8bcd71e3817e9_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133621_jpg.rf.c3887d6390bc4eff5679dbf75a4cc8d5_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134101_jpg.rf.31291d284c56619b567920454c551aef_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134912_jpg.rf.fa9ad12d1b6eec77586399144cf94d52_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133330_jpg.rf.de69efcddb15777fe221234b7399ec90_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133643_jpg.rf.6c69f3e3051a0711e1d9fcd9ae05ec32_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134056_jpg.rf.7dbf04349226ca02326439c8cb63cfd8_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133344_jpg.rf.e48cc88355eed51e52467cc0af78e13b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133826_jpg.rf.1f05c7afad87c834729c4e69cf60ba12_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133638_jpg.rf.96aeb186d920b46a12a704fece16edd0_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133656_jpg.rf.00a7cd51b1bc8474210a809df52eaac7_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133327_jpg.rf.6ad8b7bc052fe267dc6cb186f362f394_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134044_jpg.rf.3f10895ccad6ea809c916ccbf47d337d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134258_jpg.rf.b5b5e0a48f4851716aefd7995d3e7d70_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134750_jpg.rf.e796a2b61a281428b46f40cd451e9482_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133326_jpg.rf.4f05b90e1231f0a37a569ad728219b9b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_135034_jpg.rf.fce49c5fd42aff4cf8d899b8ab9138c2_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133355_jpg.rf.932836217ffce9ecc65bb050612f908f_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133353_jpg.rf.5e6f59227143fff9dbf806cfac7fad26_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133608_jpg.rf.ce798d41b7948148205776e62f76ac1d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ocr_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>image_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-MILK|B-SOY|B-PEANUT|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-SOY|O|O|B-EGG|O|B-WHEAT|O|B-PEANUT|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-SOY|B-MILK|B-PEANUT|B-EGG|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-MILK|B-SOY|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 대두, 우유, 땅콩, 달걀, 쇠고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|달걀|우유|대두|복숭아|돼지고기|쇠고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-SOY|B-EGG|B-MILK|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두, 아황산류 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두, 땅콩 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기, 토마토, 복숭아 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 대두, 계란, 우유 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|대두|우유|땅콩|달걀|쇠고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-WHEAT|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기, 복숭아 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두 함유</x:t>
+    <x:t>quality_label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제품명 고구마형과자 내용량 162 @ 식품유형| 과자(유탕처리제품) (업소명 (주) 코스모스제과 / 경기다꿀 '소저제주사 진접습 플강픽 kI http:llwww csms co (스비기한|후면표기일까지 판 "to SII [민구#말늄지국 d-토코페 '엿 딱 새 98 % , (원재료명 1 청제소 크림해 알 남압 960번길 '캐나다) '창[팔록렉인유 (발렉8,1o ; l(혼합히] 탓 콩대문(한로_ Uo; 물 글리 '씨해</x:t>
   </x:si>
   <x:si>
     <x:t>corrected_text</x:t>
   </x:si>
   <x:si>
+    <x:t>우유, 밀, 대두 함유</x:t>
+  </x:si>
+  <x:si>
     <x:t>밀|우유|대두|아황산류|함유</x:t>
   </x:si>
   <x:si>
-    <x:t>우유, 밀, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|대두|계란|우유|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|우유|대두|땅콩|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중복인데 어디인지 학인필요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기|토마토|복숭아|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>unreadable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|밀|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>readable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기|복숭아|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|돼지고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 돼지고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O|O|O</x:t>
+    <x:t>Salmif Canoylngieo desloseau and iarnkmt  manos Sugar; 3neni dmount0 u % Podu Mah NTavill Erin 영입경보 659 U망 0g 소고기 OR SAVAA 바이 c 0o시 USO 스_쏘 'horibo WWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C' o0- 도 Blenc Cr 산도 깊은 '불런드 새빵 커미 내용 ;"요| 맨맨7 "Ay 이미국심 시답 사다 0 대무구 0 10 "0o답 왜7 소들기물 '"랜-그리{ 담기 비다 럽나위 '93 '언제 브대 나두유 무리다 방' 신문 '입82s ID 벤시터 42 고함 미 반물 시고기; 햇i 본사 책미 V '주터 리시오 덮 ` 진임음수 d9 구입런 소비자3 예 또보트이금보 0 의반 내 보심 신과 F메 (서3 V 버II VM TI 디y '가사T다이 31 Y다 8: TC 29 RUASTING  GOFH 풍미의 바섯 시그니처 '이미지예 (운산' FEI 기심;임 며자 나오 IDV3IG5I "심새생 소비기인 g리BaI지_P CPn Y새Lw [가이인 드움째 영양정보 유끼 소재새 '대인터 [선생요시 [민드마루다 (알레이시야신) ug:' 비R 신어서로 @소자덧 세O스 P 기비터리 예스내e (너_=국신)) 어징래 p재기끔 P외유 iCal 가,재; '기다기공히 {아H이N야신) 그) "중어제제스비다 "드바켓자 그다자' JAL 유자 , 산도츠 니 언드 'Q어스보 a 아스기보이지적 재심국기피므두 '해다F Rl요요 P리어스; '리싸리 FPA '모라리신6다 Rr s {어디오피야신 자; 대기가 유어자금다 '밑가  '-N3다 그거하다 '피의고 NSCTII 모시 53 V시  모아지대S '구u움이 '고재상미실: Wco? (수신사요주부 V7I TBUI UD' '년N)- IUP 8882</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UU F 셈 외28고 넷애 인5 없이 집$ [바비체터 소콜러껏 후 K#a부도로 어거드t시햇로 4흉y-버{ 기입까지 무고런오 {영양장보 V추ig lial 제기 치피 {경가트 직임 정주시 `구 _로l 뜨집 미로 {진; 주월 T유-팔출로움 전문유 발a로적= 톤출히 4 미실팀 T기 -무E비럽물_하-_형 망플리 핑: (h물-턱자 팀주-물 비출님신: 식- 표로문t '가공유자 봉 (방고 분말유_ 소르  단자훨신 사리- 기터호움 스_톱 미0 U스리훨신 플로등스 진경 빚 {37j5P7 0Z3" 청트 백 감유 담 대지터 구교; 팔발: 유뜨로 쇠끼 고사( [지하 사과v 비교교t 빨- 퓨문기오자월 신 흑p 대 HACCP 두중5하다양x8 보l Z 곳 피온 커회국 한고 타스템SO '리 DAIa EWNIs DD 오기다 '부드움] I전만 {의D쉬리( '있다 I6i '방고 생명" ImD [mmMmm 플리하 만리맛 [사훨 소비 식 정요제 '매기지하신 . '발히-@오 돌레다지훨진  기루"다 '일현세 년문 전배] 퇴지부유 | [캠어터리D-스리돌 신드조절계경 스물장우지다 "뱉버V-기" '출서린 '글리리지림산-스르 (농소무해 비 트스템 | 본림히자기번 '본텔적U스물성으자 내_놈-분말 ,돼짓  영리 제로 방로j품 퍼러스 _바로회직식화 [[입거등 스썹제제식물성유자 계 제릭국 'UiJsr '80TTT7: [다? 숨기  은 l신물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50 5 제1  (국색스 Ne 밀 우유 대륙 [소비기화 |말런 또기히하집물표보고a IIYAMOe 포장재질|몰리프로필로내포장면 해태제과식품(주) / 천안2공장 (제 조원 |중법 천요스 지률- |울 n@호 [유통전문 올림언해대짚구 [길 기히하다 '용신구 컬리다 [판 매 원 및 '본 미벼 '38* #8 곳 *이 '생격 주 내내' '하안 7 k 소골되다 벌스가' 사사)  주 스틱 NKy {관틱 [제품명 [포키 극세식품유다 조골렉가공품 [원재료명 및 '당 코코아매스데덜관드산) 가공유제성가교로산  합량 | [밀가루밀호주산 소트님 떠gP 코코아버터; W? '미국신 Sv '정제소금. 유화제2 흔합제제치자황색소 유화제] '항금 8대터 산도조절제2 효모 호소제 정제수 프로미 하&amp; 이황산류 한강대로 서울특별시  충륭이 서늘히고 피하여 습기찬 곳을 '공성거대워원화  세물은 직사광선 ((KU ` '요금부럼 ( 주십시오 '수신자 보관하여 W '고객만족실: '국번없이 곳에 N3r 도미도] 피해보상 신고는 '세중온 '불랑식품 = (의거 힘으나 '있습니다 ` '부정' 구입한 '세조하고 보다하스 6677) ' #년송이 . 'U이하로 보사 및 I석예서 불하이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용세의 35버i생인 Gni 농빛 Orone 용 LOTT 1952 E내a내교레교 ESnP 퀴T [지발 재조판매인 '켓가필문 '선탕 코 늘틱 11m5 '유표움;가궁무자-거WE 국신) @대타유유 88 % 합심 남비 '구멍 심심 말 예반 03 % 곳예 진 무:  '깨내 보심 시한반 '반집이 생길 수 8 "801062' 및 #없이 녹아 히안 교민 유n 춤 '신고트 국 없이 }리늄 버문 미a '부점; 고문 마련 만 가능 유지 하 k입 제료 실이I IIUI 10o VO (영양정보 (10030306010121 {리프로-데 경기대로 진위면 '미국신 전멋 식도 법그럭 핑버시 #기인까지언 김기도 '11 920 k데랜무드(주) ` '코야분밥| 인기리밥 '딱스테다리R업 소비기 '곤함문유; (끝분변유 n유 그데스U다 R1미국신) , 소드님) (기공유지 '메y미로) 골렉기공유세싱가포고산 , 식즌유임 손입분유]  0-소비터 '?함식용유(경화유) { (정제수 합요끓} {전리객 {정비소금 손함분유유그레국내신 , {인재료임 (선탕; 가공유재싱가꾸른산) , 신M 쇼드님(기3유지; {유청단내분마 신5조 심제23, {유Y미 '기타선틱(실탕 전분) '기타코 코아가공품 플래인유) , '기타가공품 주정0  '본사계서 고남지원5터 유라세2중 변질감은 드시도 무대하다 '인헤예 '청류주0 있의u "8c26 의합 피배 '소비자기본번예 습기루 '식사관선 ' 1399 조|릿 붙람식협 '뻔심습니다: 돼지고기 { #]_자다 ZEC 야채 야채</x:t>
+  </x:si>
+  <x:si>
+    <x:t>labels</x:t>
   </x:si>
   <x:si>
     <x:t>tokens</x:t>
-  </x:si>
-  <x:si>
-    <x:t>labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인식 불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기 함유</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -326,8 +416,17 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -987,495 +1086,594 @@
   <x:dimension ref="A1:F31"/>
   <x:sheetFormatPr defaultColWidth="8.66015625" defaultRowHeight="16.399999999999999"/>
   <x:sheetData>
-    <x:row r="1" spans="1:5">
+    <x:row r="1" spans="1:6">
       <x:c r="A1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>57</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>72</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>73</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
       <x:c r="A2" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B2" t="s">
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>58</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>44</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>45</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>43</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>59</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F7" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>62</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D8" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E8" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F8" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
       <x:c r="A9" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="s">
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>5</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>46</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>4</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F9" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F10" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:6">
+      <x:c r="A12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D12" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E12" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F12" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:6">
+      <x:c r="A13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B13" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D13" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F13" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:6">
+      <x:c r="A14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:6">
+      <x:c r="A15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E15" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F16" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6">
+      <x:c r="A17" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E17" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D11" t="s">
+      <x:c r="F17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6">
+      <x:c r="A18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F18" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6">
+      <x:c r="A19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C19" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E19" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F19" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6">
+      <x:c r="A20" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E20" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F20" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:6">
+      <x:c r="A21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D21" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E21" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F21" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:6">
+      <x:c r="A22" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D22" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E22" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F22" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:6">
+      <x:c r="A23" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B23" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E23" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F23" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:6">
+      <x:c r="A24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B24" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E11" t="s">
+      <x:c r="C24" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F24" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:6">
+      <x:c r="A25" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C25" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E25" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F25" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:6">
+      <x:c r="A26" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F11" t="s">
+      <x:c r="B26" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C26" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D26" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E26" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F26" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:6">
+      <x:c r="A27" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E27" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F27" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:6">
+      <x:c r="A28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D28" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:6">
+      <x:c r="A29" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E29" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F29" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:6">
+      <x:c r="A30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:6">
+      <x:c r="A31" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D31" t="s">
         <x:v>66</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:5">
-      <x:c r="A12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E12" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:5">
-      <x:c r="A13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D13" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E13" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5">
-      <x:c r="A14" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:5">
-      <x:c r="A15" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:5">
-      <x:c r="A16" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C16" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:5">
-      <x:c r="A17" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:5">
-      <x:c r="A18" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B18" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E18" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5">
-      <x:c r="A19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B19" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C19" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D19" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E19" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:5">
-      <x:c r="A20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B20" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E20" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:5">
-      <x:c r="A21" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D21" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E21" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:5">
-      <x:c r="A22" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C22" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:5">
-      <x:c r="A23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B23" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C23" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D23" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E23" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:5">
-      <x:c r="A24" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B24" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E24" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:5">
-      <x:c r="A25" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B25" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E25" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:5">
-      <x:c r="A26" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B26" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E26" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:5">
-      <x:c r="A27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B27" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C27" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D27" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E27" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:5">
-      <x:c r="A28" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B28" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C28" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D28" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E28" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:5">
-      <x:c r="A29" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B29" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C29" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D29" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E29" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:5">
-      <x:c r="A30" t="s">
+      <x:c r="E31" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B30" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D30" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E30" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:5">
-      <x:c r="A31" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B31" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C31" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D31" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E31" t="s">
-        <x:v>66</x:v>
+      <x:c r="F31" t="s">
+        <x:v>87</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
